--- a/sample-data/아이돌 출퇴근 정보/Samildol_external_activity_records.xlsx
+++ b/sample-data/아이돌 출퇴근 정보/Samildol_external_activity_records.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="Rc1392303f1f240b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R05c13ded5aef4d2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="Ra29098a5829f47af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="R3a61dcc85f4448fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R39295c0b26094adf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="Rd96ce3197f124039"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36,7 +36,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -46,6 +46,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1F7A8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -69,7 +74,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -77,6 +82,18 @@
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -687,6 +704,446 @@
         <x:v>콘서트 리허설</x:v>
       </x:c>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="12" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="str">
+        <x:v>Haru</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="str">
+        <x:v>ATT-20260711-001</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="str">
+        <x:v>팬미팅 연습 입실</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="12" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B22" s="11" t="str">
+        <x:v>Min</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D22" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="str">
+        <x:v>ATT-20260711-002</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="str">
+        <x:v>팬미팅 연습 입실</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="12" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="str">
+        <x:v>Seo</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="str">
+        <x:v>ATT-20260711-003</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="str">
+        <x:v>팬미팅 연습 입실</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="12" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B24" s="11" t="str">
+        <x:v>Lia</x:v>
+      </x:c>
+      <x:c r="C24" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D24" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="str">
+        <x:v>ATT-20260711-004</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="str">
+        <x:v>팬미팅 연습 입실</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="12" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="str">
+        <x:v>Noa</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="str">
+        <x:v>ATT-20260711-005</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str">
+        <x:v>팬미팅 연습 입실</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="12" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B26" s="11" t="str">
+        <x:v>Haru</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="str">
+        <x:v>대기</x:v>
+      </x:c>
+      <x:c r="D26" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="str">
+        <x:v>ATT-20260712-001</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="str">
+        <x:v>콘텐츠 촬영 대기</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="12" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="str">
+        <x:v>Seo</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="str">
+        <x:v>대기</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="str">
+        <x:v>ATT-20260712-002</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="str">
+        <x:v>콘텐츠 촬영 대기</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="12" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B28" s="11" t="str">
+        <x:v>Noa</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="str">
+        <x:v>대기</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="str">
+        <x:v>ATT-20260712-003</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="str">
+        <x:v>콘텐츠 촬영 대기</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="12" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="str">
+        <x:v>Haru</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="str">
+        <x:v>ATT-20260713-001</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="str">
+        <x:v>월간 콘텐츠 회의</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="12" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="str">
+        <x:v>Min</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="str">
+        <x:v>ATT-20260713-002</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="str">
+        <x:v>월간 콘텐츠 회의</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="12" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="str">
+        <x:v>Seo</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="str">
+        <x:v>ATT-20260713-003</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>월간 콘텐츠 회의</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="12" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="str">
+        <x:v>Lia</x:v>
+      </x:c>
+      <x:c r="C32" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D32" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="str">
+        <x:v>ATT-20260713-004</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="str">
+        <x:v>월간 콘텐츠 회의</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="12" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>Noa</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="str">
+        <x:v>ATT-20260713-005</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>월간 콘텐츠 회의</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="12" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B34" s="11" t="str">
+        <x:v>Haru</x:v>
+      </x:c>
+      <x:c r="C34" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D34" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="str">
+        <x:v>ATT-20260714-001</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="str">
+        <x:v>보컬 퍼포먼스 점검</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="12" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="str">
+        <x:v>Min</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="str">
+        <x:v>ATT-20260714-002</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="str">
+        <x:v>보컬 퍼포먼스 점검</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="12" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B36" s="11" t="str">
+        <x:v>Lia</x:v>
+      </x:c>
+      <x:c r="C36" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D36" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E36" s="11" t="str">
+        <x:v>ATT-20260714-003</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="str">
+        <x:v>보컬 퍼포먼스 점검</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="12" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="str">
+        <x:v>Noa</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="str">
+        <x:v>ATT-20260714-004</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="str">
+        <x:v>보컬 퍼포먼스 점검</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="12" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B38" s="11" t="str">
+        <x:v>Haru</x:v>
+      </x:c>
+      <x:c r="C38" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D38" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="str">
+        <x:v>ATT-20260715-001</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="str">
+        <x:v>정산기간 마감 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="12" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="str">
+        <x:v>Min</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="str">
+        <x:v>ATT-20260715-002</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="str">
+        <x:v>정산기간 마감 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="12" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B40" s="11" t="str">
+        <x:v>Seo</x:v>
+      </x:c>
+      <x:c r="C40" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D40" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="str">
+        <x:v>ATT-20260715-003</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="str">
+        <x:v>정산기간 마감 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="12" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B41" s="11" t="str">
+        <x:v>Lia</x:v>
+      </x:c>
+      <x:c r="C41" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="str">
+        <x:v>ATT-20260715-004</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="str">
+        <x:v>정산기간 마감 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="12" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B42" s="11" t="str">
+        <x:v>Noa</x:v>
+      </x:c>
+      <x:c r="C42" s="11" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D42" s="11" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="str">
+        <x:v>ATT-20260715-005</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="str">
+        <x:v>정산기간 마감 리허설</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/sample-data/아이돌 출퇴근 정보/Samildol_external_activity_records.xlsx
+++ b/sample-data/아이돌 출퇴근 정보/Samildol_external_activity_records.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="R3a61dcc85f4448fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R39295c0b26094adf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="Rd96ce3197f124039"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="Rbf0873e524e54f5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R7eced13d32f4420b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="Rdf147083dd044417"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -35,8 +35,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1D252C"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -51,6 +57,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F7A8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0E6F5"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -74,7 +90,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -94,6 +110,18 @@
     <x:xf numFmtId="200" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -298,50 +326,50 @@
   <x:cols>
     <x:col min="1" max="1" width="9.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.25" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14.75" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.5" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="15" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="str">
+      <x:c r="B1" s="15" t="str">
         <x:v>멤버</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="str">
+      <x:c r="C1" s="15" t="str">
         <x:v>상태</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="str">
+      <x:c r="D1" s="15" t="str">
         <x:v>외부시스템</x:v>
       </x:c>
-      <x:c r="E1" s="4" t="str">
+      <x:c r="E1" s="15" t="str">
         <x:v>원천ID</x:v>
       </x:c>
-      <x:c r="F1" s="4" t="str">
+      <x:c r="F1" s="15" t="str">
         <x:v>비고</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5" t="n">
+      <x:c r="A2" s="16" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B2" s="2" t="str">
+      <x:c r="B2" s="17" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="str">
+      <x:c r="C2" s="17" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D2" s="17" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E2" s="17" t="str">
         <x:v>ATT-20260701-001</x:v>
       </x:c>
-      <x:c r="F2" s="2" t="str">
-        <x:v>연습실 입실</x:v>
+      <x:c r="F2" s="17" t="str">
+        <x:v>컴백 안무 연습</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -361,27 +389,27 @@
         <x:v>ATT-20260701-002</x:v>
       </x:c>
       <x:c r="F3" s="2" t="str">
-        <x:v>연습실 입실</x:v>
+        <x:v>컴백 안무 연습</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="5" t="n">
+      <x:c r="A4" s="16" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B4" s="2" t="str">
+      <x:c r="B4" s="17" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C4" s="2" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="str">
+      <x:c r="C4" s="17" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D4" s="17" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E4" s="17" t="str">
         <x:v>ATT-20260701-003</x:v>
       </x:c>
-      <x:c r="F4" s="2" t="str">
-        <x:v>연습실 입실</x:v>
+      <x:c r="F4" s="17" t="str">
+        <x:v>컴백 안무 연습</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -401,26 +429,26 @@
         <x:v>ATT-20260701-004</x:v>
       </x:c>
       <x:c r="F5" s="2" t="str">
-        <x:v>연습실 입실</x:v>
+        <x:v>컴백 안무 연습</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="5" t="n">
+      <x:c r="A6" s="16" t="n">
         <x:v>46206</x:v>
       </x:c>
-      <x:c r="B6" s="2" t="str">
+      <x:c r="B6" s="17" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C6" s="2" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D6" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E6" s="2" t="str">
-        <x:v>CAL-20260703-001</x:v>
-      </x:c>
-      <x:c r="F6" s="2" t="str">
+      <x:c r="C6" s="17" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D6" s="17" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E6" s="17" t="str">
+        <x:v>ATT-20260703-001</x:v>
+      </x:c>
+      <x:c r="F6" s="17" t="str">
         <x:v>음악 방송 사전녹화</x:v>
       </x:c>
     </x:row>
@@ -432,35 +460,35 @@
         <x:v>Min</x:v>
       </x:c>
       <x:c r="C7" s="2" t="str">
-        <x:v>외부일정</x:v>
+        <x:v>출근</x:v>
       </x:c>
       <x:c r="D7" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
+        <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E7" s="2" t="str">
-        <x:v>CAL-20260703-001</x:v>
+        <x:v>ATT-20260703-002</x:v>
       </x:c>
       <x:c r="F7" s="2" t="str">
         <x:v>음악 방송 사전녹화</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="5" t="n">
+      <x:c r="A8" s="16" t="n">
         <x:v>46206</x:v>
       </x:c>
-      <x:c r="B8" s="2" t="str">
+      <x:c r="B8" s="17" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C8" s="2" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E8" s="2" t="str">
-        <x:v>CAL-20260703-001</x:v>
-      </x:c>
-      <x:c r="F8" s="2" t="str">
+      <x:c r="C8" s="17" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D8" s="17" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E8" s="17" t="str">
+        <x:v>ATT-20260703-003</x:v>
+      </x:c>
+      <x:c r="F8" s="17" t="str">
         <x:v>음악 방송 사전녹화</x:v>
       </x:c>
     </x:row>
@@ -472,35 +500,35 @@
         <x:v>Lia</x:v>
       </x:c>
       <x:c r="C9" s="2" t="str">
-        <x:v>외부일정</x:v>
+        <x:v>출근</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
+        <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
-        <x:v>CAL-20260703-001</x:v>
+        <x:v>ATT-20260703-004</x:v>
       </x:c>
       <x:c r="F9" s="2" t="str">
         <x:v>음악 방송 사전녹화</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="5" t="n">
+      <x:c r="A10" s="16" t="n">
         <x:v>46206</x:v>
       </x:c>
-      <x:c r="B10" s="2" t="str">
+      <x:c r="B10" s="17" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C10" s="2" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E10" s="2" t="str">
-        <x:v>CAL-20260703-001</x:v>
-      </x:c>
-      <x:c r="F10" s="2" t="str">
+      <x:c r="C10" s="17" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="str">
+        <x:v>ATT-20260703-005</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="str">
         <x:v>음악 방송 사전녹화</x:v>
       </x:c>
     </x:row>
@@ -521,27 +549,27 @@
         <x:v>ATT-20260706-001</x:v>
       </x:c>
       <x:c r="F11" s="2" t="str">
-        <x:v>라디오 대기</x:v>
+        <x:v>라디오 게스트</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="5" t="n">
+      <x:c r="A12" s="16" t="n">
         <x:v>46209</x:v>
       </x:c>
-      <x:c r="B12" s="2" t="str">
+      <x:c r="B12" s="17" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C12" s="2" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E12" s="2" t="str">
+      <x:c r="C12" s="17" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="str">
         <x:v>ATT-20260706-002</x:v>
       </x:c>
-      <x:c r="F12" s="2" t="str">
-        <x:v>라디오 대기</x:v>
+      <x:c r="F12" s="17" t="str">
+        <x:v>라디오 게스트</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -552,35 +580,35 @@
         <x:v>Haru</x:v>
       </x:c>
       <x:c r="C13" s="2" t="str">
-        <x:v>외부일정</x:v>
+        <x:v>출근</x:v>
       </x:c>
       <x:c r="D13" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
+        <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E13" s="2" t="str">
-        <x:v>CAL-20260709-001</x:v>
+        <x:v>ATT-20260709-001</x:v>
       </x:c>
       <x:c r="F13" s="2" t="str">
         <x:v>안무 수정 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="5" t="n">
+      <x:c r="A14" s="16" t="n">
         <x:v>46212</x:v>
       </x:c>
-      <x:c r="B14" s="2" t="str">
+      <x:c r="B14" s="17" t="str">
         <x:v>Lia</x:v>
       </x:c>
-      <x:c r="C14" s="2" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D14" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E14" s="2" t="str">
-        <x:v>CAL-20260709-001</x:v>
-      </x:c>
-      <x:c r="F14" s="2" t="str">
+      <x:c r="C14" s="17" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="str">
+        <x:v>ATT-20260709-002</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="str">
         <x:v>안무 수정 리허설</x:v>
       </x:c>
     </x:row>
@@ -592,121 +620,121 @@
         <x:v>Noa</x:v>
       </x:c>
       <x:c r="C15" s="2" t="str">
-        <x:v>외부일정</x:v>
+        <x:v>출근</x:v>
       </x:c>
       <x:c r="D15" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
+        <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E15" s="2" t="str">
-        <x:v>CAL-20260709-001</x:v>
+        <x:v>ATT-20260709-003</x:v>
       </x:c>
       <x:c r="F15" s="2" t="str">
         <x:v>안무 수정 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="5" t="n">
-        <x:v>46213</x:v>
-      </x:c>
-      <x:c r="B16" s="2" t="str">
+      <x:c r="A16" s="16" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B16" s="17" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C16" s="2" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D16" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E16" s="2" t="str">
-        <x:v>CAL-20260710-001</x:v>
-      </x:c>
-      <x:c r="F16" s="2" t="str">
-        <x:v>콘서트 리허설</x:v>
+      <x:c r="C16" s="17" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="str">
+        <x:v>ATT-20260711-001</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="str">
+        <x:v>팬미팅 연습</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="5" t="n">
-        <x:v>46213</x:v>
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B17" s="2" t="str">
         <x:v>Min</x:v>
       </x:c>
       <x:c r="C17" s="2" t="str">
-        <x:v>외부일정</x:v>
+        <x:v>출근</x:v>
       </x:c>
       <x:c r="D17" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
+        <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E17" s="2" t="str">
-        <x:v>CAL-20260710-001</x:v>
+        <x:v>ATT-20260711-002</x:v>
       </x:c>
       <x:c r="F17" s="2" t="str">
-        <x:v>콘서트 리허설</x:v>
+        <x:v>팬미팅 연습</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="5" t="n">
-        <x:v>46213</x:v>
-      </x:c>
-      <x:c r="B18" s="2" t="str">
+      <x:c r="A18" s="16" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B18" s="17" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C18" s="2" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D18" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E18" s="2" t="str">
-        <x:v>CAL-20260710-001</x:v>
-      </x:c>
-      <x:c r="F18" s="2" t="str">
-        <x:v>콘서트 리허설</x:v>
+      <x:c r="C18" s="17" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="str">
+        <x:v>ATT-20260711-003</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="str">
+        <x:v>팬미팅 연습</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="5" t="n">
-        <x:v>46213</x:v>
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B19" s="2" t="str">
         <x:v>Lia</x:v>
       </x:c>
       <x:c r="C19" s="2" t="str">
-        <x:v>외부일정</x:v>
+        <x:v>출근</x:v>
       </x:c>
       <x:c r="D19" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
+        <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E19" s="2" t="str">
-        <x:v>CAL-20260710-001</x:v>
+        <x:v>ATT-20260711-004</x:v>
       </x:c>
       <x:c r="F19" s="2" t="str">
-        <x:v>콘서트 리허설</x:v>
+        <x:v>팬미팅 연습</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="5" t="n">
-        <x:v>46213</x:v>
-      </x:c>
-      <x:c r="B20" s="2" t="str">
+      <x:c r="A20" s="16" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B20" s="17" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C20" s="2" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D20" s="2" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E20" s="2" t="str">
-        <x:v>CAL-20260710-001</x:v>
-      </x:c>
-      <x:c r="F20" s="2" t="str">
-        <x:v>콘서트 리허설</x:v>
+      <x:c r="C20" s="17" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="str">
+        <x:v>ATT-20260711-005</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="str">
+        <x:v>팬미팅 연습</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="12" t="n">
-        <x:v>46214</x:v>
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B21" s="11" t="str">
         <x:v>Haru</x:v>
@@ -718,38 +746,38 @@
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
-        <x:v>ATT-20260711-001</x:v>
+        <x:v>ATT-20260712-001</x:v>
       </x:c>
       <x:c r="F21" s="11" t="str">
-        <x:v>팬미팅 연습 입실</x:v>
+        <x:v>콘텐츠 촬영</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="12" t="n">
-        <x:v>46214</x:v>
-      </x:c>
-      <x:c r="B22" s="11" t="str">
-        <x:v>Min</x:v>
-      </x:c>
-      <x:c r="C22" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D22" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E22" s="11" t="str">
-        <x:v>ATT-20260711-002</x:v>
-      </x:c>
-      <x:c r="F22" s="11" t="str">
-        <x:v>팬미팅 연습 입실</x:v>
+      <x:c r="A22" s="18" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B22" s="19" t="str">
+        <x:v>Seo</x:v>
+      </x:c>
+      <x:c r="C22" s="19" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D22" s="19" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E22" s="19" t="str">
+        <x:v>ATT-20260712-002</x:v>
+      </x:c>
+      <x:c r="F22" s="19" t="str">
+        <x:v>콘텐츠 촬영</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="12" t="n">
-        <x:v>46214</x:v>
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B23" s="11" t="str">
-        <x:v>Seo</x:v>
+        <x:v>Noa</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
         <x:v>출근</x:v>
@@ -758,38 +786,38 @@
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str">
-        <x:v>ATT-20260711-003</x:v>
+        <x:v>ATT-20260712-003</x:v>
       </x:c>
       <x:c r="F23" s="11" t="str">
-        <x:v>팬미팅 연습 입실</x:v>
+        <x:v>콘텐츠 촬영</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="12" t="n">
-        <x:v>46214</x:v>
-      </x:c>
-      <x:c r="B24" s="11" t="str">
-        <x:v>Lia</x:v>
-      </x:c>
-      <x:c r="C24" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D24" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="str">
-        <x:v>ATT-20260711-004</x:v>
-      </x:c>
-      <x:c r="F24" s="11" t="str">
-        <x:v>팬미팅 연습 입실</x:v>
+      <x:c r="A24" s="18" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B24" s="19" t="str">
+        <x:v>Haru</x:v>
+      </x:c>
+      <x:c r="C24" s="19" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D24" s="19" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E24" s="19" t="str">
+        <x:v>ATT-20260713-001</x:v>
+      </x:c>
+      <x:c r="F24" s="19" t="str">
+        <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="12" t="n">
-        <x:v>46214</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="B25" s="11" t="str">
-        <x:v>Noa</x:v>
+        <x:v>Min</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
         <x:v>출근</x:v>
@@ -798,75 +826,75 @@
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
-        <x:v>ATT-20260711-005</x:v>
+        <x:v>ATT-20260713-002</x:v>
       </x:c>
       <x:c r="F25" s="11" t="str">
-        <x:v>팬미팅 연습 입실</x:v>
+        <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="12" t="n">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="B26" s="11" t="str">
-        <x:v>Haru</x:v>
-      </x:c>
-      <x:c r="C26" s="11" t="str">
-        <x:v>대기</x:v>
-      </x:c>
-      <x:c r="D26" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="str">
-        <x:v>ATT-20260712-001</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="str">
-        <x:v>콘텐츠 촬영 대기</x:v>
+      <x:c r="A26" s="18" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B26" s="19" t="str">
+        <x:v>Seo</x:v>
+      </x:c>
+      <x:c r="C26" s="19" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D26" s="19" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E26" s="19" t="str">
+        <x:v>ATT-20260713-003</x:v>
+      </x:c>
+      <x:c r="F26" s="19" t="str">
+        <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="12" t="n">
-        <x:v>46215</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="B27" s="11" t="str">
-        <x:v>Seo</x:v>
+        <x:v>Lia</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>대기</x:v>
+        <x:v>출근</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
-        <x:v>ATT-20260712-002</x:v>
+        <x:v>ATT-20260713-004</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>콘텐츠 촬영 대기</x:v>
+        <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="12" t="n">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="B28" s="11" t="str">
+      <x:c r="A28" s="18" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B28" s="19" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C28" s="11" t="str">
-        <x:v>대기</x:v>
-      </x:c>
-      <x:c r="D28" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="str">
-        <x:v>ATT-20260712-003</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="str">
-        <x:v>콘텐츠 촬영 대기</x:v>
+      <x:c r="C28" s="19" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D28" s="19" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E28" s="19" t="str">
+        <x:v>ATT-20260713-005</x:v>
+      </x:c>
+      <x:c r="F28" s="19" t="str">
+        <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="12" t="n">
-        <x:v>46216</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="B29" s="11" t="str">
         <x:v>Haru</x:v>
@@ -878,35 +906,35 @@
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
-        <x:v>ATT-20260713-001</x:v>
+        <x:v>ATT-20260715-001</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>월간 콘텐츠 회의</x:v>
+        <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="12" t="n">
-        <x:v>46216</x:v>
-      </x:c>
-      <x:c r="B30" s="11" t="str">
+      <x:c r="A30" s="18" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B30" s="19" t="str">
         <x:v>Min</x:v>
       </x:c>
-      <x:c r="C30" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D30" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="str">
-        <x:v>ATT-20260713-002</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="str">
-        <x:v>월간 콘텐츠 회의</x:v>
+      <x:c r="C30" s="19" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D30" s="19" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E30" s="19" t="str">
+        <x:v>ATT-20260715-002</x:v>
+      </x:c>
+      <x:c r="F30" s="19" t="str">
+        <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="12" t="n">
-        <x:v>46216</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="B31" s="11" t="str">
         <x:v>Seo</x:v>
@@ -918,35 +946,35 @@
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
-        <x:v>ATT-20260713-003</x:v>
+        <x:v>ATT-20260715-003</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>월간 콘텐츠 회의</x:v>
+        <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="12" t="n">
-        <x:v>46216</x:v>
-      </x:c>
-      <x:c r="B32" s="11" t="str">
+      <x:c r="A32" s="18" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B32" s="19" t="str">
         <x:v>Lia</x:v>
       </x:c>
-      <x:c r="C32" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D32" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E32" s="11" t="str">
-        <x:v>ATT-20260713-004</x:v>
-      </x:c>
-      <x:c r="F32" s="11" t="str">
-        <x:v>월간 콘텐츠 회의</x:v>
+      <x:c r="C32" s="19" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D32" s="19" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E32" s="19" t="str">
+        <x:v>ATT-20260715-004</x:v>
+      </x:c>
+      <x:c r="F32" s="19" t="str">
+        <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="12" t="n">
-        <x:v>46216</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="B33" s="11" t="str">
         <x:v>Noa</x:v>
@@ -958,193 +986,90 @@
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>ATT-20260713-005</x:v>
+        <x:v>ATT-20260715-005</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>월간 콘텐츠 회의</x:v>
+        <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="12" t="n">
-        <x:v>46217</x:v>
-      </x:c>
-      <x:c r="B34" s="11" t="str">
-        <x:v>Haru</x:v>
-      </x:c>
-      <x:c r="C34" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D34" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E34" s="11" t="str">
-        <x:v>ATT-20260714-001</x:v>
-      </x:c>
-      <x:c r="F34" s="11" t="str">
-        <x:v>보컬 퍼포먼스 점검</x:v>
-      </x:c>
+      <x:c r="A34" s="12"/>
+      <x:c r="B34" s="11"/>
+      <x:c r="C34" s="11"/>
+      <x:c r="D34" s="11"/>
+      <x:c r="E34" s="11"/>
+      <x:c r="F34" s="11"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="12" t="n">
-        <x:v>46217</x:v>
-      </x:c>
-      <x:c r="B35" s="11" t="str">
-        <x:v>Min</x:v>
-      </x:c>
-      <x:c r="C35" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D35" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E35" s="11" t="str">
-        <x:v>ATT-20260714-002</x:v>
-      </x:c>
-      <x:c r="F35" s="11" t="str">
-        <x:v>보컬 퍼포먼스 점검</x:v>
-      </x:c>
+      <x:c r="A35" s="12"/>
+      <x:c r="B35" s="11"/>
+      <x:c r="C35" s="11"/>
+      <x:c r="D35" s="11"/>
+      <x:c r="E35" s="11"/>
+      <x:c r="F35" s="11"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="12" t="n">
-        <x:v>46217</x:v>
-      </x:c>
-      <x:c r="B36" s="11" t="str">
-        <x:v>Lia</x:v>
-      </x:c>
-      <x:c r="C36" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D36" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E36" s="11" t="str">
-        <x:v>ATT-20260714-003</x:v>
-      </x:c>
-      <x:c r="F36" s="11" t="str">
-        <x:v>보컬 퍼포먼스 점검</x:v>
-      </x:c>
+      <x:c r="A36" s="12"/>
+      <x:c r="B36" s="11"/>
+      <x:c r="C36" s="11"/>
+      <x:c r="D36" s="11"/>
+      <x:c r="E36" s="11"/>
+      <x:c r="F36" s="11"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="12" t="n">
-        <x:v>46217</x:v>
-      </x:c>
-      <x:c r="B37" s="11" t="str">
-        <x:v>Noa</x:v>
-      </x:c>
-      <x:c r="C37" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D37" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E37" s="11" t="str">
-        <x:v>ATT-20260714-004</x:v>
-      </x:c>
-      <x:c r="F37" s="11" t="str">
-        <x:v>보컬 퍼포먼스 점검</x:v>
-      </x:c>
+      <x:c r="A37" s="12"/>
+      <x:c r="B37" s="11"/>
+      <x:c r="C37" s="11"/>
+      <x:c r="D37" s="11"/>
+      <x:c r="E37" s="11"/>
+      <x:c r="F37" s="11"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="12" t="n">
-        <x:v>46218</x:v>
-      </x:c>
-      <x:c r="B38" s="11" t="str">
-        <x:v>Haru</x:v>
-      </x:c>
-      <x:c r="C38" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D38" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E38" s="11" t="str">
-        <x:v>ATT-20260715-001</x:v>
-      </x:c>
-      <x:c r="F38" s="11" t="str">
-        <x:v>정산기간 마감 리허설</x:v>
-      </x:c>
+      <x:c r="A38" s="12"/>
+      <x:c r="B38" s="11"/>
+      <x:c r="C38" s="11"/>
+      <x:c r="D38" s="11"/>
+      <x:c r="E38" s="11"/>
+      <x:c r="F38" s="11"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="12" t="n">
-        <x:v>46218</x:v>
-      </x:c>
-      <x:c r="B39" s="11" t="str">
-        <x:v>Min</x:v>
-      </x:c>
-      <x:c r="C39" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D39" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E39" s="11" t="str">
-        <x:v>ATT-20260715-002</x:v>
-      </x:c>
-      <x:c r="F39" s="11" t="str">
-        <x:v>정산기간 마감 리허설</x:v>
-      </x:c>
+      <x:c r="A39" s="12"/>
+      <x:c r="B39" s="11"/>
+      <x:c r="C39" s="11"/>
+      <x:c r="D39" s="11"/>
+      <x:c r="E39" s="11"/>
+      <x:c r="F39" s="11"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="12" t="n">
-        <x:v>46218</x:v>
-      </x:c>
-      <x:c r="B40" s="11" t="str">
-        <x:v>Seo</x:v>
-      </x:c>
-      <x:c r="C40" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D40" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E40" s="11" t="str">
-        <x:v>ATT-20260715-003</x:v>
-      </x:c>
-      <x:c r="F40" s="11" t="str">
-        <x:v>정산기간 마감 리허설</x:v>
-      </x:c>
+      <x:c r="A40" s="12"/>
+      <x:c r="B40" s="11"/>
+      <x:c r="C40" s="11"/>
+      <x:c r="D40" s="11"/>
+      <x:c r="E40" s="11"/>
+      <x:c r="F40" s="11"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="12" t="n">
-        <x:v>46218</x:v>
-      </x:c>
-      <x:c r="B41" s="11" t="str">
-        <x:v>Lia</x:v>
-      </x:c>
-      <x:c r="C41" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D41" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E41" s="11" t="str">
-        <x:v>ATT-20260715-004</x:v>
-      </x:c>
-      <x:c r="F41" s="11" t="str">
-        <x:v>정산기간 마감 리허설</x:v>
-      </x:c>
+      <x:c r="A41" s="12"/>
+      <x:c r="B41" s="11"/>
+      <x:c r="C41" s="11"/>
+      <x:c r="D41" s="11"/>
+      <x:c r="E41" s="11"/>
+      <x:c r="F41" s="11"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="12" t="n">
-        <x:v>46218</x:v>
-      </x:c>
-      <x:c r="B42" s="11" t="str">
-        <x:v>Noa</x:v>
-      </x:c>
-      <x:c r="C42" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D42" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E42" s="11" t="str">
-        <x:v>ATT-20260715-005</x:v>
-      </x:c>
-      <x:c r="F42" s="11" t="str">
-        <x:v>정산기간 마감 리허설</x:v>
-      </x:c>
+      <x:c r="A42" s="12"/>
+      <x:c r="B42" s="11"/>
+      <x:c r="C42" s="11"/>
+      <x:c r="D42" s="11"/>
+      <x:c r="E42" s="11"/>
+      <x:c r="F42" s="11"/>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="C2:C33">
+      <x:formula1>"출근,외부일정,제외"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -1155,42 +1080,42 @@
   <x:cols>
     <x:col min="1" max="1" width="9.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="10.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="15" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="str">
+      <x:c r="B1" s="15" t="str">
         <x:v>일정명</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="str">
+      <x:c r="C1" s="15" t="str">
         <x:v>참여 멤버</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="str">
+      <x:c r="D1" s="15" t="str">
         <x:v>외부시스템</x:v>
       </x:c>
-      <x:c r="E1" s="4" t="str">
+      <x:c r="E1" s="15" t="str">
         <x:v>원천ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5" t="n">
+      <x:c r="A2" s="16" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B2" s="2" t="str">
+      <x:c r="B2" s="17" t="str">
         <x:v>컴백 안무 연습</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="str">
+      <x:c r="C2" s="17" t="str">
         <x:v>Haru, Min, Seo, Lia</x:v>
       </x:c>
-      <x:c r="D2" s="2" t="str">
+      <x:c r="D2" s="17" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E2" s="2" t="str">
+      <x:c r="E2" s="17" t="str">
         <x:v>CAL-20260701-001</x:v>
       </x:c>
     </x:row>
@@ -1212,19 +1137,19 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="5" t="n">
+      <x:c r="A4" s="16" t="n">
         <x:v>46209</x:v>
       </x:c>
-      <x:c r="B4" s="2" t="str">
+      <x:c r="B4" s="17" t="str">
         <x:v>라디오 게스트</x:v>
       </x:c>
-      <x:c r="C4" s="2" t="str">
+      <x:c r="C4" s="17" t="str">
         <x:v>Min, Seo</x:v>
       </x:c>
-      <x:c r="D4" s="2" t="str">
+      <x:c r="D4" s="17" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E4" s="2" t="str">
+      <x:c r="E4" s="17" t="str">
         <x:v>CAL-20260706-001</x:v>
       </x:c>
     </x:row>
@@ -1246,20 +1171,71 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="5" t="n">
-        <x:v>46213</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="str">
-        <x:v>콘서트 리허설</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="str">
+      <x:c r="A6" s="16" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B6" s="17" t="str">
+        <x:v>팬미팅 연습</x:v>
+      </x:c>
+      <x:c r="C6" s="17" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa</x:v>
       </x:c>
-      <x:c r="D6" s="2" t="str">
+      <x:c r="D6" s="17" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E6" s="2" t="str">
-        <x:v>CAL-20260710-001</x:v>
+      <x:c r="E6" s="17" t="str">
+        <x:v>CAL-20260711-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="5" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="str">
+        <x:v>콘텐츠 촬영</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="str">
+        <x:v>Haru, Seo, Noa</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="str">
+        <x:v>CAL-20260712-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="16" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B8" s="17" t="str">
+        <x:v>월간 콘텐츠 회의</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa</x:v>
+      </x:c>
+      <x:c r="D8" s="17" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E8" s="17" t="str">
+        <x:v>CAL-20260713-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="5" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="str">
+        <x:v>마감 리허설</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E9" s="2" t="str">
+        <x:v>CAL-20260715-001</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/sample-data/아이돌 출퇴근 정보/Samildol_external_activity_records.xlsx
+++ b/sample-data/아이돌 출퇴근 정보/Samildol_external_activity_records.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="Rbf0873e524e54f5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R7eced13d32f4420b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="Rdf147083dd044417"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="Recd3f4125adc47db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R9a1a287cfbef4504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="R3683136721bf4e1b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -42,7 +42,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -57,6 +57,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F7A8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0E6F5"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -90,7 +100,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -122,6 +132,26 @@
       <x:alignment vertical="center" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -333,42 +363,42 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="15" t="str">
+      <x:c r="A1" s="22" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="15" t="str">
+      <x:c r="B1" s="22" t="str">
         <x:v>멤버</x:v>
       </x:c>
-      <x:c r="C1" s="15" t="str">
+      <x:c r="C1" s="22" t="str">
         <x:v>상태</x:v>
       </x:c>
-      <x:c r="D1" s="15" t="str">
+      <x:c r="D1" s="22" t="str">
         <x:v>외부시스템</x:v>
       </x:c>
-      <x:c r="E1" s="15" t="str">
+      <x:c r="E1" s="22" t="str">
         <x:v>원천ID</x:v>
       </x:c>
-      <x:c r="F1" s="15" t="str">
+      <x:c r="F1" s="22" t="str">
         <x:v>비고</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="16" t="n">
+      <x:c r="A2" s="23" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B2" s="17" t="str">
+      <x:c r="B2" s="24" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C2" s="17" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D2" s="17" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E2" s="17" t="str">
+      <x:c r="C2" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D2" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E2" s="24" t="str">
         <x:v>ATT-20260701-001</x:v>
       </x:c>
-      <x:c r="F2" s="17" t="str">
+      <x:c r="F2" s="24" t="str">
         <x:v>컴백 안무 연습</x:v>
       </x:c>
     </x:row>
@@ -393,22 +423,22 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="16" t="n">
+      <x:c r="A4" s="23" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B4" s="17" t="str">
+      <x:c r="B4" s="24" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C4" s="17" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D4" s="17" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E4" s="17" t="str">
+      <x:c r="C4" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D4" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E4" s="24" t="str">
         <x:v>ATT-20260701-003</x:v>
       </x:c>
-      <x:c r="F4" s="17" t="str">
+      <x:c r="F4" s="24" t="str">
         <x:v>컴백 안무 연습</x:v>
       </x:c>
     </x:row>
@@ -433,28 +463,28 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="16" t="n">
-        <x:v>46206</x:v>
-      </x:c>
-      <x:c r="B6" s="17" t="str">
+      <x:c r="A6" s="23" t="n">
+        <x:v>46205</x:v>
+      </x:c>
+      <x:c r="B6" s="24" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C6" s="17" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D6" s="17" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E6" s="17" t="str">
-        <x:v>ATT-20260703-001</x:v>
-      </x:c>
-      <x:c r="F6" s="17" t="str">
-        <x:v>음악 방송 사전녹화</x:v>
+      <x:c r="C6" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D6" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E6" s="24" t="str">
+        <x:v>ATT-20260702-001</x:v>
+      </x:c>
+      <x:c r="F6" s="24" t="str">
+        <x:v>쇼케이스 사전 점검</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="n">
-        <x:v>46206</x:v>
+        <x:v>46205</x:v>
       </x:c>
       <x:c r="B7" s="2" t="str">
         <x:v>Min</x:v>
@@ -466,35 +496,35 @@
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E7" s="2" t="str">
-        <x:v>ATT-20260703-002</x:v>
+        <x:v>ATT-20260702-002</x:v>
       </x:c>
       <x:c r="F7" s="2" t="str">
-        <x:v>음악 방송 사전녹화</x:v>
+        <x:v>쇼케이스 사전 점검</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="16" t="n">
-        <x:v>46206</x:v>
-      </x:c>
-      <x:c r="B8" s="17" t="str">
+      <x:c r="A8" s="23" t="n">
+        <x:v>46205</x:v>
+      </x:c>
+      <x:c r="B8" s="24" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C8" s="17" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D8" s="17" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E8" s="17" t="str">
-        <x:v>ATT-20260703-003</x:v>
-      </x:c>
-      <x:c r="F8" s="17" t="str">
-        <x:v>음악 방송 사전녹화</x:v>
+      <x:c r="C8" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D8" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E8" s="24" t="str">
+        <x:v>ATT-20260702-003</x:v>
+      </x:c>
+      <x:c r="F8" s="24" t="str">
+        <x:v>쇼케이스 사전 점검</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="n">
-        <x:v>46206</x:v>
+        <x:v>46205</x:v>
       </x:c>
       <x:c r="B9" s="2" t="str">
         <x:v>Lia</x:v>
@@ -506,78 +536,78 @@
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
-        <x:v>ATT-20260703-004</x:v>
+        <x:v>ATT-20260702-004</x:v>
       </x:c>
       <x:c r="F9" s="2" t="str">
-        <x:v>음악 방송 사전녹화</x:v>
+        <x:v>쇼케이스 사전 점검</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="16" t="n">
-        <x:v>46206</x:v>
-      </x:c>
-      <x:c r="B10" s="17" t="str">
+      <x:c r="A10" s="23" t="n">
+        <x:v>46205</x:v>
+      </x:c>
+      <x:c r="B10" s="24" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E10" s="17" t="str">
-        <x:v>ATT-20260703-005</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="str">
-        <x:v>음악 방송 사전녹화</x:v>
+      <x:c r="C10" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D10" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E10" s="24" t="str">
+        <x:v>ATT-20260702-005</x:v>
+      </x:c>
+      <x:c r="F10" s="24" t="str">
+        <x:v>쇼케이스 사전 점검</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="5" t="n">
-        <x:v>46209</x:v>
+        <x:v>46206</x:v>
       </x:c>
       <x:c r="B11" s="2" t="str">
+        <x:v>Haru</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="str">
+        <x:v>ATT-20260703-001</x:v>
+      </x:c>
+      <x:c r="F11" s="2" t="str">
+        <x:v>음악 방송 사전녹화</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="23" t="n">
+        <x:v>46206</x:v>
+      </x:c>
+      <x:c r="B12" s="24" t="str">
         <x:v>Min</x:v>
       </x:c>
-      <x:c r="C11" s="2" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E11" s="2" t="str">
-        <x:v>ATT-20260706-001</x:v>
-      </x:c>
-      <x:c r="F11" s="2" t="str">
-        <x:v>라디오 게스트</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="16" t="n">
-        <x:v>46209</x:v>
-      </x:c>
-      <x:c r="B12" s="17" t="str">
-        <x:v>Seo</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="str">
-        <x:v>ATT-20260706-002</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="str">
-        <x:v>라디오 게스트</x:v>
+      <x:c r="C12" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D12" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E12" s="24" t="str">
+        <x:v>ATT-20260703-002</x:v>
+      </x:c>
+      <x:c r="F12" s="24" t="str">
+        <x:v>음악 방송 사전녹화</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="5" t="n">
-        <x:v>46212</x:v>
+        <x:v>46206</x:v>
       </x:c>
       <x:c r="B13" s="2" t="str">
-        <x:v>Haru</x:v>
+        <x:v>Seo</x:v>
       </x:c>
       <x:c r="C13" s="2" t="str">
         <x:v>출근</x:v>
@@ -586,35 +616,35 @@
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E13" s="2" t="str">
-        <x:v>ATT-20260709-001</x:v>
+        <x:v>ATT-20260703-003</x:v>
       </x:c>
       <x:c r="F13" s="2" t="str">
-        <x:v>안무 수정 리허설</x:v>
+        <x:v>음악 방송 사전녹화</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="16" t="n">
-        <x:v>46212</x:v>
-      </x:c>
-      <x:c r="B14" s="17" t="str">
+      <x:c r="A14" s="23" t="n">
+        <x:v>46206</x:v>
+      </x:c>
+      <x:c r="B14" s="24" t="str">
         <x:v>Lia</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="str">
-        <x:v>ATT-20260709-002</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="str">
-        <x:v>안무 수정 리허설</x:v>
+      <x:c r="C14" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D14" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E14" s="24" t="str">
+        <x:v>ATT-20260703-004</x:v>
+      </x:c>
+      <x:c r="F14" s="24" t="str">
+        <x:v>음악 방송 사전녹화</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="5" t="n">
-        <x:v>46212</x:v>
+        <x:v>46206</x:v>
       </x:c>
       <x:c r="B15" s="2" t="str">
         <x:v>Noa</x:v>
@@ -626,38 +656,38 @@
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E15" s="2" t="str">
-        <x:v>ATT-20260709-003</x:v>
+        <x:v>ATT-20260703-005</x:v>
       </x:c>
       <x:c r="F15" s="2" t="str">
-        <x:v>안무 수정 리허설</x:v>
+        <x:v>음악 방송 사전녹화</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="16" t="n">
-        <x:v>46214</x:v>
-      </x:c>
-      <x:c r="B16" s="17" t="str">
-        <x:v>Haru</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="str">
-        <x:v>ATT-20260711-001</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="str">
-        <x:v>팬미팅 연습</x:v>
+      <x:c r="A16" s="23" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="B16" s="24" t="str">
+        <x:v>Min</x:v>
+      </x:c>
+      <x:c r="C16" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D16" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E16" s="24" t="str">
+        <x:v>ATT-20260706-001</x:v>
+      </x:c>
+      <x:c r="F16" s="24" t="str">
+        <x:v>라디오 게스트</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="5" t="n">
-        <x:v>46214</x:v>
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B17" s="2" t="str">
-        <x:v>Min</x:v>
+        <x:v>Seo</x:v>
       </x:c>
       <x:c r="C17" s="2" t="str">
         <x:v>출근</x:v>
@@ -666,407 +696,578 @@
         <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E17" s="2" t="str">
-        <x:v>ATT-20260711-002</x:v>
+        <x:v>ATT-20260706-002</x:v>
       </x:c>
       <x:c r="F17" s="2" t="str">
-        <x:v>팬미팅 연습</x:v>
+        <x:v>라디오 게스트</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="16" t="n">
-        <x:v>46214</x:v>
-      </x:c>
-      <x:c r="B18" s="17" t="str">
-        <x:v>Seo</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="str">
-        <x:v>ATT-20260711-003</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="str">
-        <x:v>팬미팅 연습</x:v>
+      <x:c r="A18" s="23" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="B18" s="24" t="str">
+        <x:v>Haru</x:v>
+      </x:c>
+      <x:c r="C18" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D18" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E18" s="24" t="str">
+        <x:v>ATT-20260707-001</x:v>
+      </x:c>
+      <x:c r="F18" s="24" t="str">
+        <x:v>브랜드 화보 촬영</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="5" t="n">
-        <x:v>46214</x:v>
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B19" s="2" t="str">
+        <x:v>Min</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D19" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E19" s="2" t="str">
+        <x:v>ATT-20260707-002</x:v>
+      </x:c>
+      <x:c r="F19" s="2" t="str">
+        <x:v>브랜드 화보 촬영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="23" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="B20" s="24" t="str">
+        <x:v>Seo</x:v>
+      </x:c>
+      <x:c r="C20" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D20" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E20" s="24" t="str">
+        <x:v>ATT-20260707-003</x:v>
+      </x:c>
+      <x:c r="F20" s="24" t="str">
+        <x:v>브랜드 화보 촬영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="5" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="B21" s="2" t="str">
         <x:v>Lia</x:v>
       </x:c>
-      <x:c r="C19" s="2" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D19" s="2" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E19" s="2" t="str">
-        <x:v>ATT-20260711-004</x:v>
-      </x:c>
-      <x:c r="F19" s="2" t="str">
-        <x:v>팬미팅 연습</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="16" t="n">
-        <x:v>46214</x:v>
-      </x:c>
-      <x:c r="B20" s="17" t="str">
+      <x:c r="C21" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D21" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E21" s="2" t="str">
+        <x:v>ATT-20260707-004</x:v>
+      </x:c>
+      <x:c r="F21" s="2" t="str">
+        <x:v>브랜드 화보 촬영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="23" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="B22" s="24" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C20" s="17" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D20" s="17" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="str">
-        <x:v>ATT-20260711-005</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="str">
-        <x:v>팬미팅 연습</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="12" t="n">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="B21" s="11" t="str">
+      <x:c r="C22" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D22" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E22" s="24" t="str">
+        <x:v>ATT-20260707-005</x:v>
+      </x:c>
+      <x:c r="F22" s="24" t="str">
+        <x:v>브랜드 화보 촬영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="5" t="n">
+        <x:v>46211</x:v>
+      </x:c>
+      <x:c r="B23" s="2" t="str">
+        <x:v>Seo</x:v>
+      </x:c>
+      <x:c r="C23" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D23" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E23" s="2" t="str">
+        <x:v>ATT-20260708-001</x:v>
+      </x:c>
+      <x:c r="F23" s="2" t="str">
+        <x:v>드라마 카메오 촬영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="23" t="n">
+        <x:v>46212</x:v>
+      </x:c>
+      <x:c r="B24" s="24" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D21" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="str">
-        <x:v>ATT-20260712-001</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="str">
-        <x:v>콘텐츠 촬영</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="18" t="n">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="B22" s="19" t="str">
+      <x:c r="C24" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D24" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E24" s="24" t="str">
+        <x:v>ATT-20260709-001</x:v>
+      </x:c>
+      <x:c r="F24" s="24" t="str">
+        <x:v>안무 수정 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="5" t="n">
+        <x:v>46212</x:v>
+      </x:c>
+      <x:c r="B25" s="2" t="str">
+        <x:v>Lia</x:v>
+      </x:c>
+      <x:c r="C25" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D25" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E25" s="2" t="str">
+        <x:v>ATT-20260709-002</x:v>
+      </x:c>
+      <x:c r="F25" s="2" t="str">
+        <x:v>안무 수정 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="23" t="n">
+        <x:v>46212</x:v>
+      </x:c>
+      <x:c r="B26" s="24" t="str">
+        <x:v>Noa</x:v>
+      </x:c>
+      <x:c r="C26" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D26" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E26" s="24" t="str">
+        <x:v>ATT-20260709-003</x:v>
+      </x:c>
+      <x:c r="F26" s="24" t="str">
+        <x:v>안무 수정 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="5" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B27" s="2" t="str">
+        <x:v>Haru</x:v>
+      </x:c>
+      <x:c r="C27" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D27" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E27" s="2" t="str">
+        <x:v>ATT-20260710-001</x:v>
+      </x:c>
+      <x:c r="F27" s="2" t="str">
+        <x:v>콘서트 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="23" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B28" s="24" t="str">
+        <x:v>Min</x:v>
+      </x:c>
+      <x:c r="C28" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D28" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E28" s="24" t="str">
+        <x:v>ATT-20260710-002</x:v>
+      </x:c>
+      <x:c r="F28" s="24" t="str">
+        <x:v>콘서트 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="5" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B29" s="2" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C22" s="19" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D22" s="19" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E22" s="19" t="str">
-        <x:v>ATT-20260712-002</x:v>
-      </x:c>
-      <x:c r="F22" s="19" t="str">
-        <x:v>콘텐츠 촬영</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="12" t="n">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="B23" s="11" t="str">
+      <x:c r="C29" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D29" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E29" s="2" t="str">
+        <x:v>ATT-20260710-003</x:v>
+      </x:c>
+      <x:c r="F29" s="2" t="str">
+        <x:v>콘서트 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="23" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B30" s="24" t="str">
+        <x:v>Lia</x:v>
+      </x:c>
+      <x:c r="C30" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D30" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E30" s="24" t="str">
+        <x:v>ATT-20260710-004</x:v>
+      </x:c>
+      <x:c r="F30" s="24" t="str">
+        <x:v>콘서트 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="5" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B31" s="2" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D23" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="str">
-        <x:v>ATT-20260712-003</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="str">
-        <x:v>콘텐츠 촬영</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="18" t="n">
+      <x:c r="C31" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D31" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E31" s="2" t="str">
+        <x:v>ATT-20260710-005</x:v>
+      </x:c>
+      <x:c r="F31" s="2" t="str">
+        <x:v>콘서트 리허설</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="23" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B24" s="19" t="str">
+      <x:c r="B32" s="24" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C24" s="19" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D24" s="19" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E24" s="19" t="str">
+      <x:c r="C32" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D32" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E32" s="24" t="str">
         <x:v>ATT-20260713-001</x:v>
       </x:c>
-      <x:c r="F24" s="19" t="str">
+      <x:c r="F32" s="24" t="str">
         <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="12" t="n">
+    <x:row r="33">
+      <x:c r="A33" s="5" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B25" s="11" t="str">
+      <x:c r="B33" s="2" t="str">
         <x:v>Min</x:v>
       </x:c>
-      <x:c r="C25" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D25" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="str">
+      <x:c r="C33" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D33" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E33" s="2" t="str">
         <x:v>ATT-20260713-002</x:v>
       </x:c>
-      <x:c r="F25" s="11" t="str">
+      <x:c r="F33" s="2" t="str">
         <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="18" t="n">
+    <x:row r="34">
+      <x:c r="A34" s="23" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B26" s="19" t="str">
+      <x:c r="B34" s="24" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C26" s="19" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D26" s="19" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E26" s="19" t="str">
+      <x:c r="C34" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D34" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E34" s="24" t="str">
         <x:v>ATT-20260713-003</x:v>
       </x:c>
-      <x:c r="F26" s="19" t="str">
+      <x:c r="F34" s="24" t="str">
         <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="12" t="n">
+    <x:row r="35">
+      <x:c r="A35" s="5" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B27" s="11" t="str">
+      <x:c r="B35" s="2" t="str">
         <x:v>Lia</x:v>
       </x:c>
-      <x:c r="C27" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D27" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="str">
+      <x:c r="C35" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D35" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E35" s="2" t="str">
         <x:v>ATT-20260713-004</x:v>
       </x:c>
-      <x:c r="F27" s="11" t="str">
+      <x:c r="F35" s="2" t="str">
         <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="18" t="n">
+    <x:row r="36">
+      <x:c r="A36" s="23" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B28" s="19" t="str">
+      <x:c r="B36" s="24" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C28" s="19" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D28" s="19" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E28" s="19" t="str">
+      <x:c r="C36" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D36" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E36" s="24" t="str">
         <x:v>ATT-20260713-005</x:v>
       </x:c>
-      <x:c r="F28" s="19" t="str">
+      <x:c r="F36" s="24" t="str">
         <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="12" t="n">
+    <x:row r="37">
+      <x:c r="A37" s="5" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B37" s="2" t="str">
+        <x:v>Haru</x:v>
+      </x:c>
+      <x:c r="C37" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D37" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E37" s="2" t="str">
+        <x:v>ATT-20260714-001</x:v>
+      </x:c>
+      <x:c r="F37" s="2" t="str">
+        <x:v>보컬 퍼포먼스 점검</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="23" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B38" s="24" t="str">
+        <x:v>Min</x:v>
+      </x:c>
+      <x:c r="C38" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D38" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E38" s="24" t="str">
+        <x:v>ATT-20260714-002</x:v>
+      </x:c>
+      <x:c r="F38" s="24" t="str">
+        <x:v>보컬 퍼포먼스 점검</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="5" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B39" s="2" t="str">
+        <x:v>Lia</x:v>
+      </x:c>
+      <x:c r="C39" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D39" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E39" s="2" t="str">
+        <x:v>ATT-20260714-003</x:v>
+      </x:c>
+      <x:c r="F39" s="2" t="str">
+        <x:v>보컬 퍼포먼스 점검</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="23" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B40" s="24" t="str">
+        <x:v>Noa</x:v>
+      </x:c>
+      <x:c r="C40" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D40" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E40" s="24" t="str">
+        <x:v>ATT-20260714-004</x:v>
+      </x:c>
+      <x:c r="F40" s="24" t="str">
+        <x:v>보컬 퍼포먼스 점검</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="5" t="n">
         <x:v>46218</x:v>
       </x:c>
-      <x:c r="B29" s="11" t="str">
+      <x:c r="B41" s="2" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C29" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D29" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="str">
+      <x:c r="C41" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D41" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E41" s="2" t="str">
         <x:v>ATT-20260715-001</x:v>
       </x:c>
-      <x:c r="F29" s="11" t="str">
+      <x:c r="F41" s="2" t="str">
         <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="18" t="n">
+    <x:row r="42">
+      <x:c r="A42" s="23" t="n">
         <x:v>46218</x:v>
       </x:c>
-      <x:c r="B30" s="19" t="str">
+      <x:c r="B42" s="24" t="str">
         <x:v>Min</x:v>
       </x:c>
-      <x:c r="C30" s="19" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D30" s="19" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E30" s="19" t="str">
+      <x:c r="C42" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D42" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E42" s="24" t="str">
         <x:v>ATT-20260715-002</x:v>
       </x:c>
-      <x:c r="F30" s="19" t="str">
+      <x:c r="F42" s="24" t="str">
         <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="12" t="n">
+    <x:row r="43">
+      <x:c r="A43" s="5" t="n">
         <x:v>46218</x:v>
       </x:c>
-      <x:c r="B31" s="11" t="str">
+      <x:c r="B43" s="2" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C31" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D31" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="str">
+      <x:c r="C43" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D43" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E43" s="2" t="str">
         <x:v>ATT-20260715-003</x:v>
       </x:c>
-      <x:c r="F31" s="11" t="str">
+      <x:c r="F43" s="2" t="str">
         <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="18" t="n">
+    <x:row r="44">
+      <x:c r="A44" s="23" t="n">
         <x:v>46218</x:v>
       </x:c>
-      <x:c r="B32" s="19" t="str">
+      <x:c r="B44" s="24" t="str">
         <x:v>Lia</x:v>
       </x:c>
-      <x:c r="C32" s="19" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D32" s="19" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E32" s="19" t="str">
+      <x:c r="C44" s="24" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D44" s="24" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E44" s="24" t="str">
         <x:v>ATT-20260715-004</x:v>
       </x:c>
-      <x:c r="F32" s="19" t="str">
+      <x:c r="F44" s="24" t="str">
         <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="12" t="n">
+    <x:row r="45">
+      <x:c r="A45" s="5" t="n">
         <x:v>46218</x:v>
       </x:c>
-      <x:c r="B33" s="11" t="str">
+      <x:c r="B45" s="2" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C33" s="11" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D33" s="11" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E33" s="11" t="str">
+      <x:c r="C45" s="2" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D45" s="2" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E45" s="2" t="str">
         <x:v>ATT-20260715-005</x:v>
       </x:c>
-      <x:c r="F33" s="11" t="str">
+      <x:c r="F45" s="2" t="str">
         <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="12"/>
-      <x:c r="B34" s="11"/>
-      <x:c r="C34" s="11"/>
-      <x:c r="D34" s="11"/>
-      <x:c r="E34" s="11"/>
-      <x:c r="F34" s="11"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="12"/>
-      <x:c r="B35" s="11"/>
-      <x:c r="C35" s="11"/>
-      <x:c r="D35" s="11"/>
-      <x:c r="E35" s="11"/>
-      <x:c r="F35" s="11"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="12"/>
-      <x:c r="B36" s="11"/>
-      <x:c r="C36" s="11"/>
-      <x:c r="D36" s="11"/>
-      <x:c r="E36" s="11"/>
-      <x:c r="F36" s="11"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="12"/>
-      <x:c r="B37" s="11"/>
-      <x:c r="C37" s="11"/>
-      <x:c r="D37" s="11"/>
-      <x:c r="E37" s="11"/>
-      <x:c r="F37" s="11"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="12"/>
-      <x:c r="B38" s="11"/>
-      <x:c r="C38" s="11"/>
-      <x:c r="D38" s="11"/>
-      <x:c r="E38" s="11"/>
-      <x:c r="F38" s="11"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="12"/>
-      <x:c r="B39" s="11"/>
-      <x:c r="C39" s="11"/>
-      <x:c r="D39" s="11"/>
-      <x:c r="E39" s="11"/>
-      <x:c r="F39" s="11"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="12"/>
-      <x:c r="B40" s="11"/>
-      <x:c r="C40" s="11"/>
-      <x:c r="D40" s="11"/>
-      <x:c r="E40" s="11"/>
-      <x:c r="F40" s="11"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="12"/>
-      <x:c r="B41" s="11"/>
-      <x:c r="C41" s="11"/>
-      <x:c r="D41" s="11"/>
-      <x:c r="E41" s="11"/>
-      <x:c r="F41" s="11"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="12"/>
-      <x:c r="B42" s="11"/>
-      <x:c r="C42" s="11"/>
-      <x:c r="D42" s="11"/>
-      <x:c r="E42" s="11"/>
-      <x:c r="F42" s="11"/>
-    </x:row>
   </x:sheetData>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="C2:C33">
+      <x:formula1>"출근,외부일정,제외"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C2:C45">
       <x:formula1>"출근,외부일정,제외"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1086,45 +1287,45 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="15" t="str">
+      <x:c r="A1" s="22" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="15" t="str">
+      <x:c r="B1" s="22" t="str">
         <x:v>일정명</x:v>
       </x:c>
-      <x:c r="C1" s="15" t="str">
+      <x:c r="C1" s="22" t="str">
         <x:v>참여 멤버</x:v>
       </x:c>
-      <x:c r="D1" s="15" t="str">
+      <x:c r="D1" s="22" t="str">
         <x:v>외부시스템</x:v>
       </x:c>
-      <x:c r="E1" s="15" t="str">
+      <x:c r="E1" s="22" t="str">
         <x:v>원천ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="16" t="n">
+      <x:c r="A2" s="23" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B2" s="17" t="str">
+      <x:c r="B2" s="24" t="str">
         <x:v>컴백 안무 연습</x:v>
       </x:c>
-      <x:c r="C2" s="17" t="str">
+      <x:c r="C2" s="24" t="str">
         <x:v>Haru, Min, Seo, Lia</x:v>
       </x:c>
-      <x:c r="D2" s="17" t="str">
+      <x:c r="D2" s="24" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E2" s="17" t="str">
+      <x:c r="E2" s="24" t="str">
         <x:v>CAL-20260701-001</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="n">
-        <x:v>46206</x:v>
+        <x:v>46205</x:v>
       </x:c>
       <x:c r="B3" s="2" t="str">
-        <x:v>음악 방송 사전녹화</x:v>
+        <x:v>쇼케이스 사전 점검</x:v>
       </x:c>
       <x:c r="C3" s="2" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa</x:v>
@@ -1133,100 +1334,100 @@
         <x:v>그룹 캘린더</x:v>
       </x:c>
       <x:c r="E3" s="2" t="str">
+        <x:v>CAL-20260702-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="23" t="n">
+        <x:v>46206</x:v>
+      </x:c>
+      <x:c r="B4" s="24" t="str">
+        <x:v>음악 방송 사전녹화</x:v>
+      </x:c>
+      <x:c r="C4" s="24" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa</x:v>
+      </x:c>
+      <x:c r="D4" s="24" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E4" s="24" t="str">
         <x:v>CAL-20260703-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="16" t="n">
-        <x:v>46209</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>라디오 게스트</x:v>
-      </x:c>
-      <x:c r="C4" s="17" t="str">
-        <x:v>Min, Seo</x:v>
-      </x:c>
-      <x:c r="D4" s="17" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E4" s="17" t="str">
-        <x:v>CAL-20260706-001</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="n">
-        <x:v>46212</x:v>
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B5" s="2" t="str">
-        <x:v>안무 수정 리허설</x:v>
+        <x:v>라디오 게스트</x:v>
       </x:c>
       <x:c r="C5" s="2" t="str">
-        <x:v>Haru, Lia, Noa</x:v>
+        <x:v>Min, Seo</x:v>
       </x:c>
       <x:c r="D5" s="2" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
       <x:c r="E5" s="2" t="str">
-        <x:v>CAL-20260709-001</x:v>
+        <x:v>CAL-20260706-001</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="16" t="n">
-        <x:v>46214</x:v>
-      </x:c>
-      <x:c r="B6" s="17" t="str">
-        <x:v>팬미팅 연습</x:v>
-      </x:c>
-      <x:c r="C6" s="17" t="str">
+      <x:c r="A6" s="23" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="B6" s="24" t="str">
+        <x:v>브랜드 화보 촬영</x:v>
+      </x:c>
+      <x:c r="C6" s="24" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa</x:v>
       </x:c>
-      <x:c r="D6" s="17" t="str">
+      <x:c r="D6" s="24" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E6" s="17" t="str">
-        <x:v>CAL-20260711-001</x:v>
+      <x:c r="E6" s="24" t="str">
+        <x:v>CAL-20260707-001</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="n">
-        <x:v>46215</x:v>
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B7" s="2" t="str">
-        <x:v>콘텐츠 촬영</x:v>
+        <x:v>드라마 카메오 촬영</x:v>
       </x:c>
       <x:c r="C7" s="2" t="str">
-        <x:v>Haru, Seo, Noa</x:v>
+        <x:v>Seo</x:v>
       </x:c>
       <x:c r="D7" s="2" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
       <x:c r="E7" s="2" t="str">
-        <x:v>CAL-20260712-001</x:v>
+        <x:v>CAL-20260708-001</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="16" t="n">
-        <x:v>46216</x:v>
-      </x:c>
-      <x:c r="B8" s="17" t="str">
-        <x:v>월간 콘텐츠 회의</x:v>
-      </x:c>
-      <x:c r="C8" s="17" t="str">
-        <x:v>Haru, Min, Seo, Lia, Noa</x:v>
-      </x:c>
-      <x:c r="D8" s="17" t="str">
+      <x:c r="A8" s="23" t="n">
+        <x:v>46212</x:v>
+      </x:c>
+      <x:c r="B8" s="24" t="str">
+        <x:v>안무 수정 리허설</x:v>
+      </x:c>
+      <x:c r="C8" s="24" t="str">
+        <x:v>Haru, Lia, Noa</x:v>
+      </x:c>
+      <x:c r="D8" s="24" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E8" s="17" t="str">
-        <x:v>CAL-20260713-001</x:v>
+      <x:c r="E8" s="24" t="str">
+        <x:v>CAL-20260709-001</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="n">
-        <x:v>46218</x:v>
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B9" s="2" t="str">
-        <x:v>마감 리허설</x:v>
+        <x:v>콘서트 리허설</x:v>
       </x:c>
       <x:c r="C9" s="2" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa</x:v>
@@ -1235,6 +1436,57 @@
         <x:v>그룹 캘린더</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
+        <x:v>CAL-20260710-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="23" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B10" s="24" t="str">
+        <x:v>월간 콘텐츠 회의</x:v>
+      </x:c>
+      <x:c r="C10" s="24" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa</x:v>
+      </x:c>
+      <x:c r="D10" s="24" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E10" s="24" t="str">
+        <x:v>CAL-20260713-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="5" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="str">
+        <x:v>보컬 퍼포먼스 점검</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>Haru, Min, Lia, Noa</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="str">
+        <x:v>CAL-20260714-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="23" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B12" s="24" t="str">
+        <x:v>마감 리허설</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa</x:v>
+      </x:c>
+      <x:c r="D12" s="24" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E12" s="24" t="str">
         <x:v>CAL-20260715-001</x:v>
       </x:c>
     </x:row>
@@ -1248,95 +1500,325 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="6.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="7.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="22" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="str">
+      <x:c r="B1" s="22" t="str">
+        <x:v>결제 시간</x:v>
+      </x:c>
+      <x:c r="C1" s="22" t="str">
         <x:v>내역</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="str">
+      <x:c r="D1" s="22" t="str">
         <x:v>금액</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="str">
+      <x:c r="E1" s="28" t="str">
+        <x:v>예상 식사인원</x:v>
+      </x:c>
+      <x:c r="F1" s="28" t="str">
+        <x:v>정산 제외</x:v>
+      </x:c>
+      <x:c r="G1" s="22" t="str">
         <x:v>결제수단</x:v>
       </x:c>
-      <x:c r="E1" s="4" t="str">
+      <x:c r="H1" s="22" t="str">
         <x:v>원천ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5" t="n">
+      <x:c r="A2" s="23" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B2" s="2" t="str">
+      <x:c r="B2" s="26" t="str">
+        <x:v>12:00</x:v>
+      </x:c>
+      <x:c r="C2" s="24" t="str">
         <x:v>배민 연습실 식사</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="n">
+      <x:c r="D2" s="25" t="n">
         <x:v>92000</x:v>
       </x:c>
-      <x:c r="D2" s="2" t="str">
+      <x:c r="E2" s="29" t="str">
+        <x:v>Haru, Min, Seo, Lia, Manager Park</x:v>
+      </x:c>
+      <x:c r="F2" s="29" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G2" s="24" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="E2" s="2" t="str">
+      <x:c r="H2" s="24" t="str">
         <x:v>PAY-20260701-001</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="n">
+        <x:v>46205</x:v>
+      </x:c>
+      <x:c r="B3" s="27" t="str">
+        <x:v>12:20</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="str">
+        <x:v>쇼케이스 준비 점심</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="n">
+        <x:v>125000</x:v>
+      </x:c>
+      <x:c r="E3" s="30" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
+      </x:c>
+      <x:c r="F3" s="30" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H3" s="2" t="str">
+        <x:v>PAY-20260702-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="23" t="n">
         <x:v>46206</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="str">
+      <x:c r="B4" s="26" t="str">
+        <x:v>12:00</x:v>
+      </x:c>
+      <x:c r="C4" s="24" t="str">
         <x:v>음악방송 도시락</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="n">
+      <x:c r="D4" s="25" t="n">
         <x:v>165000</x:v>
       </x:c>
-      <x:c r="D3" s="2" t="str">
+      <x:c r="E4" s="29" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
+      </x:c>
+      <x:c r="F4" s="29" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G4" s="24" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="E3" s="2" t="str">
+      <x:c r="H4" s="24" t="str">
         <x:v>PAY-20260703-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="5" t="n">
-        <x:v>46209</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="str">
-        <x:v>라디오 대기 간식</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="n">
-        <x:v>48000</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="str">
-        <x:v>배달앱</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="str">
-        <x:v>PAY-20260706-001</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="n">
+        <x:v>46209</x:v>
+      </x:c>
+      <x:c r="B5" s="27" t="str">
+        <x:v>12:00</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="str">
+        <x:v>라디오 대기 간식</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="n">
+        <x:v>48000</x:v>
+      </x:c>
+      <x:c r="E5" s="30" t="str">
+        <x:v>Min, Seo, Manager Park</x:v>
+      </x:c>
+      <x:c r="F5" s="30" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G5" s="2" t="str">
+        <x:v>배달앱</x:v>
+      </x:c>
+      <x:c r="H5" s="2" t="str">
+        <x:v>PAY-20260706-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="23" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="B6" s="26" t="str">
+        <x:v>12:40</x:v>
+      </x:c>
+      <x:c r="C6" s="24" t="str">
+        <x:v>화보 촬영 점심</x:v>
+      </x:c>
+      <x:c r="D6" s="25" t="n">
+        <x:v>135000</x:v>
+      </x:c>
+      <x:c r="E6" s="29" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
+      </x:c>
+      <x:c r="F6" s="29" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G6" s="24" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H6" s="24" t="str">
+        <x:v>PAY-20260707-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="5" t="n">
+        <x:v>46211</x:v>
+      </x:c>
+      <x:c r="B7" s="27" t="str">
+        <x:v>13:10</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="str">
+        <x:v>카메오 촬영 식사</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="E7" s="30" t="str">
+        <x:v>Seo, Manager Park</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G7" s="2" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H7" s="2" t="str">
+        <x:v>PAY-20260708-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="23" t="n">
         <x:v>46212</x:v>
       </x:c>
-      <x:c r="B5" s="2" t="str">
+      <x:c r="B8" s="26" t="str">
+        <x:v>12:00</x:v>
+      </x:c>
+      <x:c r="C8" s="24" t="str">
         <x:v>안무 연습 일식</x:v>
       </x:c>
-      <x:c r="C5" s="6" t="n">
+      <x:c r="D8" s="25" t="n">
         <x:v>74000</x:v>
       </x:c>
-      <x:c r="D5" s="2" t="str">
+      <x:c r="E8" s="29" t="str">
+        <x:v>Haru, Lia, Noa, Manager Park</x:v>
+      </x:c>
+      <x:c r="F8" s="29" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G8" s="24" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="E5" s="2" t="str">
+      <x:c r="H8" s="24" t="str">
         <x:v>PAY-20260709-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="5" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B9" s="27" t="str">
+        <x:v>18:20</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="str">
+        <x:v>콘서트 리허설 저녁</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="n">
+        <x:v>150000</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
+      </x:c>
+      <x:c r="F9" s="30" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G9" s="2" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H9" s="2" t="str">
+        <x:v>PAY-20260710-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="23" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B10" s="26" t="str">
+        <x:v>13:00</x:v>
+      </x:c>
+      <x:c r="C10" s="24" t="str">
+        <x:v>월간회의 점심</x:v>
+      </x:c>
+      <x:c r="D10" s="25" t="n">
+        <x:v>138000</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G10" s="24" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H10" s="24" t="str">
+        <x:v>PAY-20260713-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="5" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B11" s="27" t="str">
+        <x:v>12:25</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>퍼포먼스 점검 점심</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="n">
+        <x:v>104000</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="str">
+        <x:v>Haru, Min, Lia, Noa, Manager Park</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G11" s="2" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H11" s="2" t="str">
+        <x:v>PAY-20260714-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="23" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B12" s="26" t="str">
+        <x:v>18:20</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="str">
+        <x:v>마감 리허설 저녁</x:v>
+      </x:c>
+      <x:c r="D12" s="25" t="n">
+        <x:v>175000</x:v>
+      </x:c>
+      <x:c r="E12" s="29" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G12" s="24" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H12" s="24" t="str">
+        <x:v>PAY-20260715-001</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/sample-data/아이돌 출퇴근 정보/Samildol_external_activity_records.xlsx
+++ b/sample-data/아이돌 출퇴근 정보/Samildol_external_activity_records.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="Recd3f4125adc47db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R9a1a287cfbef4504"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="R3683136721bf4e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="R44d75e9d85154c53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R1ae8e9e1eabb460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="Rc0f9b68019f4433a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -42,7 +42,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -57,6 +57,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F7A8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0E6F5"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -100,7 +110,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="39">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -150,6 +160,20 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -363,42 +387,42 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="22" t="str">
+      <x:c r="A1" s="32" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="22" t="str">
+      <x:c r="B1" s="32" t="str">
         <x:v>멤버</x:v>
       </x:c>
-      <x:c r="C1" s="22" t="str">
+      <x:c r="C1" s="32" t="str">
         <x:v>상태</x:v>
       </x:c>
-      <x:c r="D1" s="22" t="str">
+      <x:c r="D1" s="32" t="str">
         <x:v>외부시스템</x:v>
       </x:c>
-      <x:c r="E1" s="22" t="str">
+      <x:c r="E1" s="32" t="str">
         <x:v>원천ID</x:v>
       </x:c>
-      <x:c r="F1" s="22" t="str">
+      <x:c r="F1" s="32" t="str">
         <x:v>비고</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="23" t="n">
+      <x:c r="A2" s="33" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B2" s="24" t="str">
+      <x:c r="B2" s="34" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C2" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D2" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E2" s="24" t="str">
+      <x:c r="C2" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D2" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E2" s="34" t="str">
         <x:v>ATT-20260701-001</x:v>
       </x:c>
-      <x:c r="F2" s="24" t="str">
+      <x:c r="F2" s="34" t="str">
         <x:v>컴백 안무 연습</x:v>
       </x:c>
     </x:row>
@@ -423,22 +447,22 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="23" t="n">
+      <x:c r="A4" s="33" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B4" s="24" t="str">
+      <x:c r="B4" s="34" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C4" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D4" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E4" s="24" t="str">
+      <x:c r="C4" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D4" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E4" s="34" t="str">
         <x:v>ATT-20260701-003</x:v>
       </x:c>
-      <x:c r="F4" s="24" t="str">
+      <x:c r="F4" s="34" t="str">
         <x:v>컴백 안무 연습</x:v>
       </x:c>
     </x:row>
@@ -463,22 +487,22 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="23" t="n">
+      <x:c r="A6" s="33" t="n">
         <x:v>46205</x:v>
       </x:c>
-      <x:c r="B6" s="24" t="str">
+      <x:c r="B6" s="34" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C6" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D6" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E6" s="24" t="str">
+      <x:c r="C6" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D6" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E6" s="34" t="str">
         <x:v>ATT-20260702-001</x:v>
       </x:c>
-      <x:c r="F6" s="24" t="str">
+      <x:c r="F6" s="34" t="str">
         <x:v>쇼케이스 사전 점검</x:v>
       </x:c>
     </x:row>
@@ -503,22 +527,22 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="23" t="n">
+      <x:c r="A8" s="33" t="n">
         <x:v>46205</x:v>
       </x:c>
-      <x:c r="B8" s="24" t="str">
+      <x:c r="B8" s="34" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C8" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D8" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E8" s="24" t="str">
+      <x:c r="C8" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="str">
         <x:v>ATT-20260702-003</x:v>
       </x:c>
-      <x:c r="F8" s="24" t="str">
+      <x:c r="F8" s="34" t="str">
         <x:v>쇼케이스 사전 점검</x:v>
       </x:c>
     </x:row>
@@ -543,22 +567,22 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="23" t="n">
+      <x:c r="A10" s="33" t="n">
         <x:v>46205</x:v>
       </x:c>
-      <x:c r="B10" s="24" t="str">
+      <x:c r="B10" s="34" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C10" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E10" s="24" t="str">
+      <x:c r="C10" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D10" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E10" s="34" t="str">
         <x:v>ATT-20260702-005</x:v>
       </x:c>
-      <x:c r="F10" s="24" t="str">
+      <x:c r="F10" s="34" t="str">
         <x:v>쇼케이스 사전 점검</x:v>
       </x:c>
     </x:row>
@@ -583,22 +607,22 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="23" t="n">
+      <x:c r="A12" s="33" t="n">
         <x:v>46206</x:v>
       </x:c>
-      <x:c r="B12" s="24" t="str">
+      <x:c r="B12" s="34" t="str">
         <x:v>Min</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D12" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E12" s="24" t="str">
+      <x:c r="C12" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D12" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E12" s="34" t="str">
         <x:v>ATT-20260703-002</x:v>
       </x:c>
-      <x:c r="F12" s="24" t="str">
+      <x:c r="F12" s="34" t="str">
         <x:v>음악 방송 사전녹화</x:v>
       </x:c>
     </x:row>
@@ -623,22 +647,22 @@
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="23" t="n">
+      <x:c r="A14" s="33" t="n">
         <x:v>46206</x:v>
       </x:c>
-      <x:c r="B14" s="24" t="str">
+      <x:c r="B14" s="34" t="str">
         <x:v>Lia</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D14" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E14" s="24" t="str">
+      <x:c r="C14" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D14" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E14" s="34" t="str">
         <x:v>ATT-20260703-004</x:v>
       </x:c>
-      <x:c r="F14" s="24" t="str">
+      <x:c r="F14" s="34" t="str">
         <x:v>음악 방송 사전녹화</x:v>
       </x:c>
     </x:row>
@@ -663,22 +687,22 @@
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="23" t="n">
+      <x:c r="A16" s="33" t="n">
         <x:v>46209</x:v>
       </x:c>
-      <x:c r="B16" s="24" t="str">
+      <x:c r="B16" s="34" t="str">
         <x:v>Min</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D16" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E16" s="24" t="str">
+      <x:c r="C16" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D16" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E16" s="34" t="str">
         <x:v>ATT-20260706-001</x:v>
       </x:c>
-      <x:c r="F16" s="24" t="str">
+      <x:c r="F16" s="34" t="str">
         <x:v>라디오 게스트</x:v>
       </x:c>
     </x:row>
@@ -703,22 +727,22 @@
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="23" t="n">
+      <x:c r="A18" s="33" t="n">
         <x:v>46210</x:v>
       </x:c>
-      <x:c r="B18" s="24" t="str">
+      <x:c r="B18" s="34" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C18" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E18" s="24" t="str">
+      <x:c r="C18" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D18" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E18" s="34" t="str">
         <x:v>ATT-20260707-001</x:v>
       </x:c>
-      <x:c r="F18" s="24" t="str">
+      <x:c r="F18" s="34" t="str">
         <x:v>브랜드 화보 촬영</x:v>
       </x:c>
     </x:row>
@@ -743,22 +767,22 @@
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="23" t="n">
+      <x:c r="A20" s="33" t="n">
         <x:v>46210</x:v>
       </x:c>
-      <x:c r="B20" s="24" t="str">
+      <x:c r="B20" s="34" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C20" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D20" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E20" s="24" t="str">
+      <x:c r="C20" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D20" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E20" s="34" t="str">
         <x:v>ATT-20260707-003</x:v>
       </x:c>
-      <x:c r="F20" s="24" t="str">
+      <x:c r="F20" s="34" t="str">
         <x:v>브랜드 화보 촬영</x:v>
       </x:c>
     </x:row>
@@ -783,22 +807,22 @@
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="23" t="n">
+      <x:c r="A22" s="33" t="n">
         <x:v>46210</x:v>
       </x:c>
-      <x:c r="B22" s="24" t="str">
+      <x:c r="B22" s="34" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C22" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D22" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E22" s="24" t="str">
+      <x:c r="C22" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D22" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E22" s="34" t="str">
         <x:v>ATT-20260707-005</x:v>
       </x:c>
-      <x:c r="F22" s="24" t="str">
+      <x:c r="F22" s="34" t="str">
         <x:v>브랜드 화보 촬영</x:v>
       </x:c>
     </x:row>
@@ -823,22 +847,22 @@
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="23" t="n">
+      <x:c r="A24" s="33" t="n">
         <x:v>46212</x:v>
       </x:c>
-      <x:c r="B24" s="24" t="str">
+      <x:c r="B24" s="34" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C24" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D24" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E24" s="24" t="str">
+      <x:c r="C24" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D24" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E24" s="34" t="str">
         <x:v>ATT-20260709-001</x:v>
       </x:c>
-      <x:c r="F24" s="24" t="str">
+      <x:c r="F24" s="34" t="str">
         <x:v>안무 수정 리허설</x:v>
       </x:c>
     </x:row>
@@ -863,22 +887,22 @@
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="23" t="n">
+      <x:c r="A26" s="33" t="n">
         <x:v>46212</x:v>
       </x:c>
-      <x:c r="B26" s="24" t="str">
+      <x:c r="B26" s="34" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C26" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D26" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E26" s="24" t="str">
+      <x:c r="C26" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D26" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E26" s="34" t="str">
         <x:v>ATT-20260709-003</x:v>
       </x:c>
-      <x:c r="F26" s="24" t="str">
+      <x:c r="F26" s="34" t="str">
         <x:v>안무 수정 리허설</x:v>
       </x:c>
     </x:row>
@@ -903,22 +927,22 @@
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="23" t="n">
+      <x:c r="A28" s="33" t="n">
         <x:v>46213</x:v>
       </x:c>
-      <x:c r="B28" s="24" t="str">
+      <x:c r="B28" s="34" t="str">
         <x:v>Min</x:v>
       </x:c>
-      <x:c r="C28" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D28" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E28" s="24" t="str">
+      <x:c r="C28" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D28" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E28" s="34" t="str">
         <x:v>ATT-20260710-002</x:v>
       </x:c>
-      <x:c r="F28" s="24" t="str">
+      <x:c r="F28" s="34" t="str">
         <x:v>콘서트 리허설</x:v>
       </x:c>
     </x:row>
@@ -943,22 +967,22 @@
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="23" t="n">
+      <x:c r="A30" s="33" t="n">
         <x:v>46213</x:v>
       </x:c>
-      <x:c r="B30" s="24" t="str">
+      <x:c r="B30" s="34" t="str">
         <x:v>Lia</x:v>
       </x:c>
-      <x:c r="C30" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D30" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E30" s="24" t="str">
+      <x:c r="C30" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D30" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E30" s="34" t="str">
         <x:v>ATT-20260710-004</x:v>
       </x:c>
-      <x:c r="F30" s="24" t="str">
+      <x:c r="F30" s="34" t="str">
         <x:v>콘서트 리허설</x:v>
       </x:c>
     </x:row>
@@ -983,22 +1007,22 @@
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="23" t="n">
+      <x:c r="A32" s="33" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B32" s="24" t="str">
+      <x:c r="B32" s="34" t="str">
         <x:v>Haru</x:v>
       </x:c>
-      <x:c r="C32" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D32" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E32" s="24" t="str">
+      <x:c r="C32" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D32" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E32" s="34" t="str">
         <x:v>ATT-20260713-001</x:v>
       </x:c>
-      <x:c r="F32" s="24" t="str">
+      <x:c r="F32" s="34" t="str">
         <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
@@ -1023,22 +1047,22 @@
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="23" t="n">
+      <x:c r="A34" s="33" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B34" s="24" t="str">
+      <x:c r="B34" s="34" t="str">
         <x:v>Seo</x:v>
       </x:c>
-      <x:c r="C34" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D34" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E34" s="24" t="str">
+      <x:c r="C34" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D34" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E34" s="34" t="str">
         <x:v>ATT-20260713-003</x:v>
       </x:c>
-      <x:c r="F34" s="24" t="str">
+      <x:c r="F34" s="34" t="str">
         <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
@@ -1063,22 +1087,22 @@
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="23" t="n">
+      <x:c r="A36" s="33" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B36" s="24" t="str">
+      <x:c r="B36" s="34" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C36" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D36" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E36" s="24" t="str">
+      <x:c r="C36" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D36" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E36" s="34" t="str">
         <x:v>ATT-20260713-005</x:v>
       </x:c>
-      <x:c r="F36" s="24" t="str">
+      <x:c r="F36" s="34" t="str">
         <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
     </x:row>
@@ -1103,22 +1127,22 @@
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="23" t="n">
+      <x:c r="A38" s="33" t="n">
         <x:v>46217</x:v>
       </x:c>
-      <x:c r="B38" s="24" t="str">
+      <x:c r="B38" s="34" t="str">
         <x:v>Min</x:v>
       </x:c>
-      <x:c r="C38" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D38" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E38" s="24" t="str">
+      <x:c r="C38" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D38" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E38" s="34" t="str">
         <x:v>ATT-20260714-002</x:v>
       </x:c>
-      <x:c r="F38" s="24" t="str">
+      <x:c r="F38" s="34" t="str">
         <x:v>보컬 퍼포먼스 점검</x:v>
       </x:c>
     </x:row>
@@ -1143,22 +1167,22 @@
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="23" t="n">
+      <x:c r="A40" s="33" t="n">
         <x:v>46217</x:v>
       </x:c>
-      <x:c r="B40" s="24" t="str">
+      <x:c r="B40" s="34" t="str">
         <x:v>Noa</x:v>
       </x:c>
-      <x:c r="C40" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D40" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E40" s="24" t="str">
+      <x:c r="C40" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D40" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E40" s="34" t="str">
         <x:v>ATT-20260714-004</x:v>
       </x:c>
-      <x:c r="F40" s="24" t="str">
+      <x:c r="F40" s="34" t="str">
         <x:v>보컬 퍼포먼스 점검</x:v>
       </x:c>
     </x:row>
@@ -1183,22 +1207,22 @@
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="23" t="n">
+      <x:c r="A42" s="33" t="n">
         <x:v>46218</x:v>
       </x:c>
-      <x:c r="B42" s="24" t="str">
+      <x:c r="B42" s="34" t="str">
         <x:v>Min</x:v>
       </x:c>
-      <x:c r="C42" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D42" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E42" s="24" t="str">
+      <x:c r="C42" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D42" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E42" s="34" t="str">
         <x:v>ATT-20260715-002</x:v>
       </x:c>
-      <x:c r="F42" s="24" t="str">
+      <x:c r="F42" s="34" t="str">
         <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
@@ -1223,22 +1247,22 @@
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="23" t="n">
+      <x:c r="A44" s="33" t="n">
         <x:v>46218</x:v>
       </x:c>
-      <x:c r="B44" s="24" t="str">
+      <x:c r="B44" s="34" t="str">
         <x:v>Lia</x:v>
       </x:c>
-      <x:c r="C44" s="24" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D44" s="24" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E44" s="24" t="str">
+      <x:c r="C44" s="34" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D44" s="34" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E44" s="34" t="str">
         <x:v>ATT-20260715-004</x:v>
       </x:c>
-      <x:c r="F44" s="24" t="str">
+      <x:c r="F44" s="34" t="str">
         <x:v>마감 리허설</x:v>
       </x:c>
     </x:row>
@@ -1287,36 +1311,36 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="22" t="str">
+      <x:c r="A1" s="32" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="22" t="str">
+      <x:c r="B1" s="32" t="str">
         <x:v>일정명</x:v>
       </x:c>
-      <x:c r="C1" s="22" t="str">
+      <x:c r="C1" s="32" t="str">
         <x:v>참여 멤버</x:v>
       </x:c>
-      <x:c r="D1" s="22" t="str">
+      <x:c r="D1" s="32" t="str">
         <x:v>외부시스템</x:v>
       </x:c>
-      <x:c r="E1" s="22" t="str">
+      <x:c r="E1" s="32" t="str">
         <x:v>원천ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="23" t="n">
+      <x:c r="A2" s="33" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B2" s="24" t="str">
+      <x:c r="B2" s="34" t="str">
         <x:v>컴백 안무 연습</x:v>
       </x:c>
-      <x:c r="C2" s="24" t="str">
+      <x:c r="C2" s="34" t="str">
         <x:v>Haru, Min, Seo, Lia</x:v>
       </x:c>
-      <x:c r="D2" s="24" t="str">
+      <x:c r="D2" s="34" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E2" s="24" t="str">
+      <x:c r="E2" s="34" t="str">
         <x:v>CAL-20260701-001</x:v>
       </x:c>
     </x:row>
@@ -1338,19 +1362,19 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="23" t="n">
+      <x:c r="A4" s="33" t="n">
         <x:v>46206</x:v>
       </x:c>
-      <x:c r="B4" s="24" t="str">
+      <x:c r="B4" s="34" t="str">
         <x:v>음악 방송 사전녹화</x:v>
       </x:c>
-      <x:c r="C4" s="24" t="str">
+      <x:c r="C4" s="34" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa</x:v>
       </x:c>
-      <x:c r="D4" s="24" t="str">
+      <x:c r="D4" s="34" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E4" s="24" t="str">
+      <x:c r="E4" s="34" t="str">
         <x:v>CAL-20260703-001</x:v>
       </x:c>
     </x:row>
@@ -1372,19 +1396,19 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="23" t="n">
+      <x:c r="A6" s="33" t="n">
         <x:v>46210</x:v>
       </x:c>
-      <x:c r="B6" s="24" t="str">
+      <x:c r="B6" s="34" t="str">
         <x:v>브랜드 화보 촬영</x:v>
       </x:c>
-      <x:c r="C6" s="24" t="str">
+      <x:c r="C6" s="34" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa</x:v>
       </x:c>
-      <x:c r="D6" s="24" t="str">
+      <x:c r="D6" s="34" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E6" s="24" t="str">
+      <x:c r="E6" s="34" t="str">
         <x:v>CAL-20260707-001</x:v>
       </x:c>
     </x:row>
@@ -1406,19 +1430,19 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="23" t="n">
+      <x:c r="A8" s="33" t="n">
         <x:v>46212</x:v>
       </x:c>
-      <x:c r="B8" s="24" t="str">
+      <x:c r="B8" s="34" t="str">
         <x:v>안무 수정 리허설</x:v>
       </x:c>
-      <x:c r="C8" s="24" t="str">
+      <x:c r="C8" s="34" t="str">
         <x:v>Haru, Lia, Noa</x:v>
       </x:c>
-      <x:c r="D8" s="24" t="str">
+      <x:c r="D8" s="34" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E8" s="24" t="str">
+      <x:c r="E8" s="34" t="str">
         <x:v>CAL-20260709-001</x:v>
       </x:c>
     </x:row>
@@ -1440,19 +1464,19 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="23" t="n">
+      <x:c r="A10" s="33" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B10" s="24" t="str">
+      <x:c r="B10" s="34" t="str">
         <x:v>월간 콘텐츠 회의</x:v>
       </x:c>
-      <x:c r="C10" s="24" t="str">
+      <x:c r="C10" s="34" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa</x:v>
       </x:c>
-      <x:c r="D10" s="24" t="str">
+      <x:c r="D10" s="34" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E10" s="24" t="str">
+      <x:c r="E10" s="34" t="str">
         <x:v>CAL-20260713-001</x:v>
       </x:c>
     </x:row>
@@ -1474,19 +1498,19 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="23" t="n">
+      <x:c r="A12" s="33" t="n">
         <x:v>46218</x:v>
       </x:c>
-      <x:c r="B12" s="24" t="str">
+      <x:c r="B12" s="34" t="str">
         <x:v>마감 리허설</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="str">
+      <x:c r="C12" s="34" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa</x:v>
       </x:c>
-      <x:c r="D12" s="24" t="str">
+      <x:c r="D12" s="34" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E12" s="24" t="str">
+      <x:c r="E12" s="34" t="str">
         <x:v>CAL-20260715-001</x:v>
       </x:c>
     </x:row>
@@ -1510,54 +1534,54 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="22" t="str">
+      <x:c r="A1" s="32" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="22" t="str">
+      <x:c r="B1" s="32" t="str">
         <x:v>결제 시간</x:v>
       </x:c>
-      <x:c r="C1" s="22" t="str">
+      <x:c r="C1" s="32" t="str">
         <x:v>내역</x:v>
       </x:c>
-      <x:c r="D1" s="22" t="str">
+      <x:c r="D1" s="32" t="str">
         <x:v>금액</x:v>
       </x:c>
-      <x:c r="E1" s="28" t="str">
+      <x:c r="E1" s="37" t="str">
         <x:v>예상 식사인원</x:v>
       </x:c>
-      <x:c r="F1" s="28" t="str">
+      <x:c r="F1" s="37" t="str">
         <x:v>정산 제외</x:v>
       </x:c>
-      <x:c r="G1" s="22" t="str">
+      <x:c r="G1" s="32" t="str">
         <x:v>결제수단</x:v>
       </x:c>
-      <x:c r="H1" s="22" t="str">
+      <x:c r="H1" s="32" t="str">
         <x:v>원천ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="23" t="n">
+      <x:c r="A2" s="33" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B2" s="26" t="str">
+      <x:c r="B2" s="36" t="str">
         <x:v>12:00</x:v>
       </x:c>
-      <x:c r="C2" s="24" t="str">
+      <x:c r="C2" s="34" t="str">
         <x:v>배민 연습실 식사</x:v>
       </x:c>
-      <x:c r="D2" s="25" t="n">
+      <x:c r="D2" s="35" t="n">
         <x:v>92000</x:v>
       </x:c>
-      <x:c r="E2" s="29" t="str">
+      <x:c r="E2" s="38" t="str">
         <x:v>Haru, Min, Seo, Lia, Manager Park</x:v>
       </x:c>
-      <x:c r="F2" s="29" t="str">
+      <x:c r="F2" s="38" t="str">
         <x:v>Manager Park</x:v>
       </x:c>
-      <x:c r="G2" s="24" t="str">
+      <x:c r="G2" s="34" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="H2" s="24" t="str">
+      <x:c r="H2" s="34" t="str">
         <x:v>PAY-20260701-001</x:v>
       </x:c>
     </x:row>
@@ -1588,28 +1612,28 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="23" t="n">
+      <x:c r="A4" s="33" t="n">
         <x:v>46206</x:v>
       </x:c>
-      <x:c r="B4" s="26" t="str">
+      <x:c r="B4" s="36" t="str">
         <x:v>12:00</x:v>
       </x:c>
-      <x:c r="C4" s="24" t="str">
+      <x:c r="C4" s="34" t="str">
         <x:v>음악방송 도시락</x:v>
       </x:c>
-      <x:c r="D4" s="25" t="n">
+      <x:c r="D4" s="35" t="n">
         <x:v>165000</x:v>
       </x:c>
-      <x:c r="E4" s="29" t="str">
+      <x:c r="E4" s="38" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
       </x:c>
-      <x:c r="F4" s="29" t="str">
+      <x:c r="F4" s="38" t="str">
         <x:v>Manager Park</x:v>
       </x:c>
-      <x:c r="G4" s="24" t="str">
+      <x:c r="G4" s="34" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="H4" s="24" t="str">
+      <x:c r="H4" s="34" t="str">
         <x:v>PAY-20260703-001</x:v>
       </x:c>
     </x:row>
@@ -1640,28 +1664,28 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="23" t="n">
+      <x:c r="A6" s="33" t="n">
         <x:v>46210</x:v>
       </x:c>
-      <x:c r="B6" s="26" t="str">
+      <x:c r="B6" s="36" t="str">
         <x:v>12:40</x:v>
       </x:c>
-      <x:c r="C6" s="24" t="str">
+      <x:c r="C6" s="34" t="str">
         <x:v>화보 촬영 점심</x:v>
       </x:c>
-      <x:c r="D6" s="25" t="n">
+      <x:c r="D6" s="35" t="n">
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="E6" s="29" t="str">
+      <x:c r="E6" s="38" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
       </x:c>
-      <x:c r="F6" s="29" t="str">
+      <x:c r="F6" s="38" t="str">
         <x:v>Manager Park</x:v>
       </x:c>
-      <x:c r="G6" s="24" t="str">
+      <x:c r="G6" s="34" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="H6" s="24" t="str">
+      <x:c r="H6" s="34" t="str">
         <x:v>PAY-20260707-001</x:v>
       </x:c>
     </x:row>
@@ -1692,28 +1716,28 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="23" t="n">
+      <x:c r="A8" s="33" t="n">
         <x:v>46212</x:v>
       </x:c>
-      <x:c r="B8" s="26" t="str">
+      <x:c r="B8" s="36" t="str">
         <x:v>12:00</x:v>
       </x:c>
-      <x:c r="C8" s="24" t="str">
+      <x:c r="C8" s="34" t="str">
         <x:v>안무 연습 일식</x:v>
       </x:c>
-      <x:c r="D8" s="25" t="n">
+      <x:c r="D8" s="35" t="n">
         <x:v>74000</x:v>
       </x:c>
-      <x:c r="E8" s="29" t="str">
+      <x:c r="E8" s="38" t="str">
         <x:v>Haru, Lia, Noa, Manager Park</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="str">
+      <x:c r="F8" s="38" t="str">
         <x:v>Manager Park</x:v>
       </x:c>
-      <x:c r="G8" s="24" t="str">
+      <x:c r="G8" s="34" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="H8" s="24" t="str">
+      <x:c r="H8" s="34" t="str">
         <x:v>PAY-20260709-001</x:v>
       </x:c>
     </x:row>
@@ -1744,28 +1768,28 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="23" t="n">
+      <x:c r="A10" s="33" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B10" s="26" t="str">
+      <x:c r="B10" s="36" t="str">
         <x:v>13:00</x:v>
       </x:c>
-      <x:c r="C10" s="24" t="str">
+      <x:c r="C10" s="34" t="str">
         <x:v>월간회의 점심</x:v>
       </x:c>
-      <x:c r="D10" s="25" t="n">
+      <x:c r="D10" s="35" t="n">
         <x:v>138000</x:v>
       </x:c>
-      <x:c r="E10" s="29" t="str">
+      <x:c r="E10" s="38" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
       </x:c>
-      <x:c r="F10" s="29" t="str">
+      <x:c r="F10" s="38" t="str">
         <x:v>Manager Park</x:v>
       </x:c>
-      <x:c r="G10" s="24" t="str">
+      <x:c r="G10" s="34" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="H10" s="24" t="str">
+      <x:c r="H10" s="34" t="str">
         <x:v>PAY-20260713-001</x:v>
       </x:c>
     </x:row>
@@ -1796,29 +1820,107 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="23" t="n">
+      <x:c r="A12" s="33" t="n">
         <x:v>46218</x:v>
       </x:c>
-      <x:c r="B12" s="26" t="str">
+      <x:c r="B12" s="36" t="str">
+        <x:v>12:05</x:v>
+      </x:c>
+      <x:c r="C12" s="34" t="str">
+        <x:v>마감 리허설 점심</x:v>
+      </x:c>
+      <x:c r="D12" s="35" t="n">
+        <x:v>125000</x:v>
+      </x:c>
+      <x:c r="E12" s="38" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
+      </x:c>
+      <x:c r="F12" s="38" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G12" s="34" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H12" s="34" t="str">
+        <x:v>PAY-20260715-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="5" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B13" s="27" t="str">
+        <x:v>12:30</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="str">
+        <x:v>마감 리허설 추가 음료</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G13" s="2" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H13" s="2" t="str">
+        <x:v>PAY-20260715-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="33" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B14" s="36" t="str">
+        <x:v>12:50</x:v>
+      </x:c>
+      <x:c r="C14" s="34" t="str">
+        <x:v>마감 리허설 간식 결제</x:v>
+      </x:c>
+      <x:c r="D14" s="35" t="n">
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="E14" s="38" t="str">
+        <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
+      </x:c>
+      <x:c r="F14" s="38" t="str">
+        <x:v>Manager Park</x:v>
+      </x:c>
+      <x:c r="G14" s="34" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H14" s="34" t="str">
+        <x:v>PAY-20260715-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="5" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B15" s="27" t="str">
         <x:v>18:20</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="str">
+      <x:c r="C15" s="2" t="str">
         <x:v>마감 리허설 저녁</x:v>
       </x:c>
-      <x:c r="D12" s="25" t="n">
+      <x:c r="D15" s="6" t="n">
         <x:v>175000</x:v>
       </x:c>
-      <x:c r="E12" s="29" t="str">
+      <x:c r="E15" s="30" t="str">
         <x:v>Haru, Min, Seo, Lia, Noa, Manager Park</x:v>
       </x:c>
-      <x:c r="F12" s="29" t="str">
+      <x:c r="F15" s="30" t="str">
         <x:v>Manager Park</x:v>
       </x:c>
-      <x:c r="G12" s="24" t="str">
+      <x:c r="G15" s="2" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="H12" s="24" t="str">
-        <x:v>PAY-20260715-001</x:v>
+      <x:c r="H15" s="2" t="str">
+        <x:v>PAY-20260715-004</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
